--- a/October_WhatsApp_Campaign_Plan.xlsx
+++ b/October_WhatsApp_Campaign_Plan.xlsx
@@ -571,7 +571,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Customer may swap any box for another (OPEN: does swapping in Clouds (8 KD) cost +1 KD?)</t>
+          <t>Customer may swap any box; swapping in Sugar Clouds makes it 20 KD</t>
         </is>
       </c>
     </row>
